--- a/data/trans_camb/IP16A08-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A08-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,95; 14,42</t>
+          <t>-12,46; 14,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,52; -2,84</t>
+          <t>-24,31; -2,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,58; -2,92</t>
+          <t>-24,49; -2,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 13,8</t>
+          <t>-17,02; 15,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 27,86</t>
+          <t>-14,87; 28,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 24,21</t>
+          <t>-13,48; 22,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 10,36</t>
+          <t>-10,73; 10,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 4,9</t>
+          <t>-14,17; 5,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 9,14</t>
+          <t>-12,56; 7,85</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-80,02; 379,47</t>
+          <t>-79,86; 346,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 537,01</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 3,85</t>
+          <t>-14,83; 4,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 4,83</t>
+          <t>-13,47; 6,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,46; -1,95</t>
+          <t>-19,66; -2,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 0,65</t>
+          <t>-16,1; 1,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 7,54</t>
+          <t>-12,16; 6,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,0; -0,29</t>
+          <t>-18,52; 0,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 0,95</t>
+          <t>-12,75; -0,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 4,01</t>
+          <t>-10,14; 3,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,29; -3,44</t>
+          <t>-16,58; -3,79</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-63,73; 27,41</t>
+          <t>-61,38; 36,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-59,78; 34,78</t>
+          <t>-54,75; 53,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-83,01; -13,58</t>
+          <t>-82,56; -13,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-65,57; 8,42</t>
+          <t>-64,69; 9,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,1; 52,2</t>
+          <t>-50,74; 45,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-68,76; 5,9</t>
+          <t>-69,61; 7,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,37; 6,19</t>
+          <t>-53,73; 0,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,02; 25,84</t>
+          <t>-44,6; 24,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-69,52; -19,56</t>
+          <t>-71,48; -23,77</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 11,67</t>
+          <t>-15,15; 10,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 23,68</t>
+          <t>-8,0; 22,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 13,52</t>
+          <t>-11,58; 13,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 15,75</t>
+          <t>-11,06; 16,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 10,12</t>
+          <t>-17,18; 9,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 4,65</t>
+          <t>-17,88; 5,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 10,33</t>
+          <t>-8,94; 9,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 11,77</t>
+          <t>-9,06; 10,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 7,05</t>
+          <t>-10,68; 6,47</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-84,4; 456,65</t>
+          <t>-85,82; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-63,68; —</t>
+          <t>-68,99; 793,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-76,71; 539,52</t>
+          <t>-77,54; 541,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-62,52; 218,4</t>
+          <t>-64,77; 281,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-85,88; 217,53</t>
+          <t>-85,84; 205,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-86,71; 89,22</t>
+          <t>-87,92; 125,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-54,01; 159,35</t>
+          <t>-55,31; 144,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,4; 184,76</t>
+          <t>-58,1; 169,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-64,98; 107,23</t>
+          <t>-67,9; 107,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 3,17</t>
+          <t>-9,8; 4,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 6,01</t>
+          <t>-9,26; 5,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,82; -0,96</t>
+          <t>-13,71; -0,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 2,55</t>
+          <t>-10,53; 2,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 5,41</t>
+          <t>-8,75; 5,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 0,86</t>
+          <t>-12,65; 0,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 1,28</t>
+          <t>-8,25; 1,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 4,17</t>
+          <t>-6,58; 3,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,34; -1,92</t>
+          <t>-11,52; -1,53</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-52,17; 27,69</t>
+          <t>-51,46; 40,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-48,12; 50,37</t>
+          <t>-47,77; 52,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-75,9; -7,28</t>
+          <t>-74,15; 0,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-51,85; 20,13</t>
+          <t>-55,02; 20,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,23; 42,58</t>
+          <t>-44,86; 46,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-63,83; 6,45</t>
+          <t>-63,46; 5,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-45,67; 9,96</t>
+          <t>-45,88; 7,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-35,38; 31,22</t>
+          <t>-35,56; 26,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-61,24; -13,65</t>
+          <t>-62,83; -12,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A08-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A08-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 14,87</t>
+          <t>-12,85; 15,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,31; -2,89</t>
+          <t>-24,13; -2,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,49; -2,9</t>
+          <t>-24,37; -2,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 15,15</t>
+          <t>-16,43; 14,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 28,12</t>
+          <t>-13,95; 26,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 22,65</t>
+          <t>-12,47; 23,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 10,81</t>
+          <t>-11,17; 9,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 5,07</t>
+          <t>-14,76; 4,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 7,85</t>
+          <t>-13,36; 7,46</t>
         </is>
       </c>
     </row>
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-79,86; 346,58</t>
+          <t>-79,56; 289,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 330,11</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 537,01</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 4,47</t>
+          <t>-14,33; 3,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 6,47</t>
+          <t>-13,52; 5,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,66; -2,05</t>
+          <t>-20,29; -1,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 1,07</t>
+          <t>-15,99; 0,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 6,97</t>
+          <t>-11,6; 7,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 0,24</t>
+          <t>-17,24; -1,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,75; -0,2</t>
+          <t>-12,23; 0,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 3,92</t>
+          <t>-8,89; 3,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,58; -3,79</t>
+          <t>-17,07; -3,54</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-61,38; 36,33</t>
+          <t>-60,53; 27,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-54,75; 53,15</t>
+          <t>-55,7; 44,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-82,56; -13,83</t>
+          <t>-83,85; -10,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-64,69; 9,66</t>
+          <t>-66,32; 7,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,74; 45,84</t>
+          <t>-48,04; 50,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,61; 7,56</t>
+          <t>-71,04; -5,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-53,73; 0,56</t>
+          <t>-53,34; 2,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,6; 24,45</t>
+          <t>-41,25; 25,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-71,48; -23,77</t>
+          <t>-72,47; -21,26</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 10,76</t>
+          <t>-14,72; 11,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 22,62</t>
+          <t>-7,78; 22,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 13,95</t>
+          <t>-11,67; 13,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 16,44</t>
+          <t>-10,57; 17,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 9,94</t>
+          <t>-16,08; 9,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,88; 5,27</t>
+          <t>-17,83; 5,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 9,78</t>
+          <t>-8,26; 11,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 10,89</t>
+          <t>-8,54; 11,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 6,47</t>
+          <t>-11,0; 7,09</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-85,82; —</t>
+          <t>-87,44; 530,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-68,99; 793,12</t>
+          <t>-67,58; 896,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,54; 541,63</t>
+          <t>-72,05; 488,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-64,77; 281,24</t>
+          <t>-66,16; 270,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-85,84; 205,1</t>
+          <t>-86,86; 165,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,92; 125,92</t>
+          <t>-88,2; 107,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,31; 144,54</t>
+          <t>-52,88; 180,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-58,1; 169,07</t>
+          <t>-55,06; 207,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-67,9; 107,74</t>
+          <t>-65,48; 135,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 4,34</t>
+          <t>-10,43; 2,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 5,87</t>
+          <t>-8,83; 6,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,71; -0,03</t>
+          <t>-14,55; -0,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 2,83</t>
+          <t>-10,1; 3,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 5,89</t>
+          <t>-9,16; 6,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 0,08</t>
+          <t>-12,32; 0,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 1,09</t>
+          <t>-8,32; 1,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 3,56</t>
+          <t>-6,44; 3,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,52; -1,53</t>
+          <t>-11,35; -1,76</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-51,46; 40,41</t>
+          <t>-54,05; 27,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-47,77; 52,28</t>
+          <t>-47,38; 55,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-74,15; 0,03</t>
+          <t>-74,8; -6,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-55,02; 20,99</t>
+          <t>-50,57; 26,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,86; 46,21</t>
+          <t>-46,5; 57,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-63,46; 5,75</t>
+          <t>-63,3; 7,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-45,88; 7,64</t>
+          <t>-44,58; 10,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-35,56; 26,06</t>
+          <t>-35,12; 31,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-62,83; -12,25</t>
+          <t>-61,72; -13,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A08-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A08-Estudios-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia</t>
+          <t>Menores que consumieron medicamentos para la alergia</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,44</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,8</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,64</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-9,1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-9,1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,8</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,35</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,1</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,32</t>
+          <t>-2,3</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 15,27</t>
+          <t>-16,25; 13,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,13; -2,89</t>
+          <t>-12,89; 27,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,37; -2,91</t>
+          <t>-12,92; 25,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 14,1</t>
+          <t>-14,95; 14,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 26,86</t>
+          <t>-21,52; -2,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 23,99</t>
+          <t>-24,58; -2,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 9,55</t>
+          <t>-10,73; 10,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 4,15</t>
+          <t>-14,91; 4,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 7,46</t>
+          <t>-11,25; 11,84</t>
         </is>
       </c>
     </row>
@@ -730,34 +730,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-5,4%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,7%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>32,14%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>5,04%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-5,4%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>28,69%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,18%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-38,25%</t>
+          <t>-26,56%</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-79,56; 289,22</t>
+          <t>-80,02; 379,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 330,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-7,18</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,43</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-8,35</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-5,11</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-3,29</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-10,44</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-7,18</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,43</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-8,6</t>
+          <t>-7,56</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-9,54</t>
+          <t>-7,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 3,3</t>
+          <t>-16,18; 0,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 5,62</t>
+          <t>-11,94; 7,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,29; -1,36</t>
+          <t>-17,0; 0,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 0,88</t>
+          <t>-15,43; 3,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 7,33</t>
+          <t>-14,73; 4,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,24; -1,06</t>
+          <t>-17,23; 1,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 0,14</t>
+          <t>-12,35; 0,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 3,81</t>
+          <t>-9,82; 4,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,07; -3,54</t>
+          <t>-14,7; -1,59</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-36,52%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-12,34%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-42,51%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-26,91%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-17,36%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-55,02%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-36,52%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-12,34%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-43,77%</t>
+          <t>-39,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-49,36%</t>
+          <t>-41,27%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-60,53; 27,47</t>
+          <t>-65,57; 8,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,7; 44,19</t>
+          <t>-50,1; 52,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-83,85; -10,77</t>
+          <t>-69,49; 6,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-66,32; 7,62</t>
+          <t>-63,73; 27,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,04; 50,34</t>
+          <t>-59,78; 34,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,04; -5,29</t>
+          <t>-68,52; 20,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-53,34; 2,36</t>
+          <t>-54,37; 6,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,25; 25,25</t>
+          <t>-44,02; 25,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-72,47; -21,26</t>
+          <t>-62,84; -8,34</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,61</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-3,35</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-4,97</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,16</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>6,95</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,15</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,61</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-3,35</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,88</t>
+          <t>3,06</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,86</t>
+          <t>-1,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 11,22</t>
+          <t>-9,95; 15,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 22,34</t>
+          <t>-15,5; 10,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 13,45</t>
+          <t>-17,01; 4,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 17,11</t>
+          <t>-15,81; 11,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 9,53</t>
+          <t>-7,63; 23,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 5,11</t>
+          <t>-11,59; 15,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 11,46</t>
+          <t>-7,9; 10,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 11,14</t>
+          <t>-8,47; 11,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 7,09</t>
+          <t>-10,29; 7,64</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>20,39%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-26,12%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-38,83%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1,78%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>76,54%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>23,68%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20,39%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-26,12%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-38,07%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-16,42%</t>
+          <t>-12,64%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-87,44; 530,69</t>
+          <t>-62,52; 218,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-67,58; 896,55</t>
+          <t>-85,88; 217,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-72,05; 488,37</t>
+          <t>-87,51; 87,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-66,16; 270,32</t>
+          <t>-84,4; 456,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-86,86; 165,02</t>
+          <t>-63,68; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-88,2; 107,02</t>
+          <t>-75,25; 603,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-52,88; 180,77</t>
+          <t>-54,01; 159,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,06; 207,13</t>
+          <t>-55,4; 184,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,48; 135,87</t>
+          <t>-63,53; 115,26</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-3,66</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,52</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-5,99</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-3,39</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-1,63</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-7,02</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-3,66</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,52</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-6,14</t>
+          <t>-4,62</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-6,6</t>
+          <t>-5,35</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 2,88</t>
+          <t>-10,52; 2,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 6,24</t>
+          <t>-8,38; 5,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,55; -0,56</t>
+          <t>-12,69; 0,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 3,05</t>
+          <t>-10,6; 3,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 6,5</t>
+          <t>-9,21; 6,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 0,71</t>
+          <t>-11,67; 2,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 1,18</t>
+          <t>-8,14; 1,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 3,9</t>
+          <t>-6,59; 4,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,35; -1,76</t>
+          <t>-10,33; -0,23</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-22,39%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-9,33%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-36,66%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-21,95%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-10,54%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-45,44%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-22,39%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-9,33%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-37,53%</t>
+          <t>-29,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-41,41%</t>
+          <t>-33,6%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-54,05; 27,86</t>
+          <t>-51,85; 20,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-47,38; 55,38</t>
+          <t>-43,23; 42,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-74,8; -6,13</t>
+          <t>-63,2; 8,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,57; 26,91</t>
+          <t>-52,17; 27,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,5; 57,34</t>
+          <t>-48,12; 50,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-63,3; 7,06</t>
+          <t>-62,25; 21,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-44,58; 10,49</t>
+          <t>-45,67; 9,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-35,12; 31,25</t>
+          <t>-35,38; 31,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-61,72; -13,68</t>
+          <t>-54,48; -0,88</t>
         </is>
       </c>
     </row>
